--- a/PPCRex/Re-test.xlsx
+++ b/PPCRex/Re-test.xlsx
@@ -27,18 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>regex</t>
   </si>
   <si>
     <t>attemptregex</t>
-  </si>
-  <si>
-    <t>abc*d</t>
-  </si>
-  <si>
-    <t>a(bc)*d</t>
   </si>
 </sst>
 </file>
@@ -1198,8 +1192,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="1"/>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="255" customWidth="1"/>
   </cols>
@@ -1212,14 +1206,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
